--- a/data/trans_dic/P55$pareja-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$pareja-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,6; 67,06</t>
+          <t>33,27; 68,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,32; 61,08</t>
+          <t>23,45; 61,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,98; 59,36</t>
+          <t>25,06; 57,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,21; 42,41</t>
+          <t>22,25; 42,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 29,13</t>
+          <t>6,87; 29,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,32; 35,07</t>
+          <t>12,43; 34,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,19; 34,36</t>
+          <t>12,31; 34,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 15,58</t>
+          <t>6,49; 15,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,23; 41,64</t>
+          <t>21,73; 42,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,8; 39,77</t>
+          <t>20,24; 39,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,17; 36,45</t>
+          <t>18,5; 37,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,25; 23,04</t>
+          <t>13,87; 23,77</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,66; 69,99</t>
+          <t>43,69; 70,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,65; 53,13</t>
+          <t>21,38; 52,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,13; 50,25</t>
+          <t>22,82; 49,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,19; 45,05</t>
+          <t>21,05; 45,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 19,01</t>
+          <t>5,02; 21,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 22,3</t>
+          <t>7,29; 23,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 28,0</t>
+          <t>8,63; 28,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,87; 22,53</t>
+          <t>11,47; 23,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,3; 38,77</t>
+          <t>21,76; 38,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,07; 29,41</t>
+          <t>13,93; 29,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,48; 32,22</t>
+          <t>15,42; 31,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,39; 27,5</t>
+          <t>16,06; 27,32</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,38; 57,27</t>
+          <t>16,36; 58,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,19; 55,57</t>
+          <t>15,96; 58,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,9; 74,57</t>
+          <t>35,32; 74,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,21; 56,85</t>
+          <t>24,22; 58,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 19,6</t>
+          <t>1,91; 18,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 29,16</t>
+          <t>8,05; 29,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 28,42</t>
+          <t>6,22; 27,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 16,48</t>
+          <t>5,22; 16,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 26,67</t>
+          <t>8,33; 25,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 33,42</t>
+          <t>14,29; 35,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,39; 40,49</t>
+          <t>17,52; 39,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,93; 26,49</t>
+          <t>13,48; 26,99</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,62; 59,23</t>
+          <t>18,55; 57,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 61,64</t>
+          <t>29,96; 63,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,23; 67,35</t>
+          <t>34,78; 68,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,23; 53,3</t>
+          <t>29,11; 52,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 18,21</t>
+          <t>4,05; 17,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 20,78</t>
+          <t>5,96; 20,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 26,83</t>
+          <t>7,55; 26,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 15,71</t>
+          <t>6,74; 15,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,71; 25,7</t>
+          <t>10,27; 25,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 32,1</t>
+          <t>14,95; 32,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,05; 36,32</t>
+          <t>17,8; 35,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,19; 24,76</t>
+          <t>15,7; 24,98</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,63; 56,61</t>
+          <t>40,84; 57,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,16; 49,13</t>
+          <t>30,49; 47,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,42; 52,5</t>
+          <t>35,67; 53,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,59; 41,75</t>
+          <t>29,3; 42,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,62</t>
+          <t>7,21; 15,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,32; 19,87</t>
+          <t>11,36; 21,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,73; 22,81</t>
+          <t>12,59; 23,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,68; 14,7</t>
+          <t>9,68; 14,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,12; 28,97</t>
+          <t>19,7; 29,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,88; 28,37</t>
+          <t>19,21; 27,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,5; 30,55</t>
+          <t>21,2; 30,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,16; 22,62</t>
+          <t>17,42; 22,56</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11720; 22717</t>
+          <t>11271; 23121</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8891; 19875</t>
+          <t>7629; 19919</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6938; 16488</t>
+          <t>6960; 15836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11023; 21047</t>
+          <t>11043; 21059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3108; 13048</t>
+          <t>3077; 13294</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7513; 21396</t>
+          <t>7581; 21280</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7331; 20665</t>
+          <t>7404; 20523</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5306; 12412</t>
+          <t>5172; 12299</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17489; 32753</t>
+          <t>17093; 33484</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18520; 37204</t>
+          <t>18928; 37079</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15972; 32049</t>
+          <t>16266; 32815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17127; 29793</t>
+          <t>17933; 30736</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20964; 33609</t>
+          <t>20980; 33667</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9884; 24258</t>
+          <t>9759; 23939</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8642; 20558</t>
+          <t>9337; 20407</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7810; 17432</t>
+          <t>8145; 17475</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2829; 12866</t>
+          <t>3401; 14330</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6476; 19699</t>
+          <t>6443; 20386</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6691; 21513</t>
+          <t>6635; 22161</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10210; 19373</t>
+          <t>9865; 20014</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25799; 44853</t>
+          <t>25180; 44715</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18858; 39404</t>
+          <t>18668; 39075</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18234; 37946</t>
+          <t>18154; 37544</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20435; 34284</t>
+          <t>20023; 34068</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3535; 12356</t>
+          <t>3531; 12660</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4244; 15526</t>
+          <t>4459; 16435</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7886; 17348</t>
+          <t>8218; 17221</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6691; 14513</t>
+          <t>6182; 14888</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>886; 9105</t>
+          <t>890; 8550</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4110; 15138</t>
+          <t>4182; 15305</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4097; 14657</t>
+          <t>3205; 14112</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2655; 9608</t>
+          <t>3043; 9375</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6237; 18148</t>
+          <t>5669; 17530</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10350; 26690</t>
+          <t>11412; 28383</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13764; 30302</t>
+          <t>13113; 29693</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10841; 22206</t>
+          <t>11302; 22631</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4996; 13686</t>
+          <t>4287; 13312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11971; 24677</t>
+          <t>11993; 25605</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9805; 19874</t>
+          <t>10264; 20219</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13067; 23042</t>
+          <t>12583; 22774</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2837; 13110</t>
+          <t>2914; 12698</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4766; 16268</t>
+          <t>4667; 16196</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6321; 21143</t>
+          <t>5954; 21022</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7360; 16382</t>
+          <t>7024; 16425</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10185; 24445</t>
+          <t>9765; 23843</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18663; 37981</t>
+          <t>17690; 38565</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19554; 39346</t>
+          <t>19276; 38057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22408; 36526</t>
+          <t>23156; 36847</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51428; 71659</t>
+          <t>51690; 72241</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45551; 71809</t>
+          <t>44567; 69964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43026; 63764</t>
+          <t>43323; 64488</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46470; 65574</t>
+          <t>46020; 66350</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16804; 36065</t>
+          <t>16649; 34700</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31646; 55542</t>
+          <t>31763; 59367</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34048; 60975</t>
+          <t>33670; 62436</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>31775; 48243</t>
+          <t>31765; 47763</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71914; 103582</t>
+          <t>70432; 104258</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84626; 120774</t>
+          <t>81765; 118811</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83602; 118789</t>
+          <t>82445; 117938</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>83271; 109756</t>
+          <t>84524; 109498</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$pareja-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$pareja-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,27; 68,25</t>
+          <t>33,7; 65,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,45; 61,22</t>
+          <t>23,43; 61,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,06; 57,01</t>
+          <t>25,12; 57,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,25; 42,43</t>
+          <t>22,37; 42,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 29,68</t>
+          <t>7,39; 30,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,43; 34,88</t>
+          <t>13,67; 35,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 34,13</t>
+          <t>12,03; 34,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 15,44</t>
+          <t>6,52; 15,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,73; 42,57</t>
+          <t>22,01; 41,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,24; 39,64</t>
+          <t>20,14; 39,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 37,33</t>
+          <t>18,91; 38,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,87; 23,77</t>
+          <t>14,17; 24,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,69; 70,11</t>
+          <t>43,38; 71,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,38; 52,43</t>
+          <t>20,59; 52,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,82; 49,88</t>
+          <t>21,82; 50,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,05; 45,17</t>
+          <t>19,55; 43,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 21,17</t>
+          <t>4,65; 19,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 23,08</t>
+          <t>7,45; 22,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 28,84</t>
+          <t>8,72; 28,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 23,27</t>
+          <t>12,74; 25,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,76; 38,65</t>
+          <t>22,07; 39,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,93; 29,16</t>
+          <t>13,21; 28,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 31,88</t>
+          <t>15,76; 32,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,06; 27,32</t>
+          <t>16,98; 28,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,36; 58,68</t>
+          <t>17,81; 58,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,96; 58,82</t>
+          <t>17,04; 58,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,32; 74,03</t>
+          <t>34,87; 73,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,22; 58,32</t>
+          <t>27,9; 59,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 18,4</t>
+          <t>1,9; 18,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 29,48</t>
+          <t>8,12; 29,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 27,37</t>
+          <t>6,57; 26,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 16,08</t>
+          <t>4,38; 15,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 25,76</t>
+          <t>9,16; 26,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,29; 35,54</t>
+          <t>13,27; 32,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 39,68</t>
+          <t>17,74; 40,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,48; 26,99</t>
+          <t>14,09; 28,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 57,61</t>
+          <t>22,24; 59,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,96; 63,96</t>
+          <t>28,62; 63,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,78; 68,52</t>
+          <t>34,02; 69,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,11; 52,68</t>
+          <t>31,43; 54,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 17,64</t>
+          <t>4,11; 18,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 20,69</t>
+          <t>5,41; 20,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 26,67</t>
+          <t>8,35; 27,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,75</t>
+          <t>7,0; 15,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 25,07</t>
+          <t>10,06; 24,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 32,6</t>
+          <t>15,89; 31,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 35,13</t>
+          <t>17,64; 35,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,7; 24,98</t>
+          <t>15,47; 25,25</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,84; 57,07</t>
+          <t>39,28; 58,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,49; 47,87</t>
+          <t>30,9; 49,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,67; 53,09</t>
+          <t>36,68; 53,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,3; 42,24</t>
+          <t>31,0; 42,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,03</t>
+          <t>7,31; 15,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 21,24</t>
+          <t>11,36; 20,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,59; 23,35</t>
+          <t>12,79; 22,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,68; 14,55</t>
+          <t>10,18; 15,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,7; 29,16</t>
+          <t>19,94; 28,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,21; 27,91</t>
+          <t>19,4; 28,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,2; 30,33</t>
+          <t>20,94; 30,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,42; 22,56</t>
+          <t>17,56; 23,16</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23760</t>
+          <t>25770</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11271; 23121</t>
+          <t>11415; 22156</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7629; 19919</t>
+          <t>7622; 19957</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6960; 15836</t>
+          <t>6977; 16108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11043; 21059</t>
+          <t>11853; 22591</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3077; 13294</t>
+          <t>3307; 13604</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7581; 21280</t>
+          <t>8337; 21589</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7404; 20523</t>
+          <t>7236; 20548</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5172; 12299</t>
+          <t>5533; 13469</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17093; 33484</t>
+          <t>17313; 33023</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18928; 37079</t>
+          <t>18837; 37262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16266; 32815</t>
+          <t>16626; 33480</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17933; 30736</t>
+          <t>19542; 33764</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26556</t>
+          <t>29971</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20980; 33667</t>
+          <t>20830; 34462</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9759; 23939</t>
+          <t>9398; 23825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9337; 20407</t>
+          <t>8926; 20651</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8145; 17475</t>
+          <t>8182; 18292</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3401; 14330</t>
+          <t>3145; 12889</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6443; 20386</t>
+          <t>6582; 19985</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6635; 22161</t>
+          <t>6703; 22160</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9865; 20014</t>
+          <t>12055; 23662</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25180; 44715</t>
+          <t>25532; 45283</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18668; 39075</t>
+          <t>17704; 38820</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18154; 37544</t>
+          <t>18560; 38391</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20023; 34068</t>
+          <t>23182; 38439</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>19092</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3531; 12660</t>
+          <t>3842; 12650</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4459; 16435</t>
+          <t>4760; 16243</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8218; 17221</t>
+          <t>8112; 17113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6182; 14888</t>
+          <t>8287; 17782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>890; 8550</t>
+          <t>883; 8635</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4182; 15305</t>
+          <t>4216; 15309</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3205; 14112</t>
+          <t>3389; 13809</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3043; 9375</t>
+          <t>2845; 10230</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5669; 17530</t>
+          <t>6233; 18256</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11412; 28383</t>
+          <t>10595; 26268</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13113; 29693</t>
+          <t>13277; 30171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11302; 22631</t>
+          <t>13330; 27322</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>31108</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4287; 13312</t>
+          <t>5139; 13721</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11993; 25605</t>
+          <t>11457; 25374</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10264; 20219</t>
+          <t>10039; 20431</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12583; 22774</t>
+          <t>14007; 24420</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2914; 12698</t>
+          <t>2960; 13307</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4667; 16196</t>
+          <t>4234; 15961</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5954; 21022</t>
+          <t>6584; 21518</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7024; 16425</t>
+          <t>7902; 17156</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9765; 23843</t>
+          <t>9564; 23342</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17690; 38565</t>
+          <t>18800; 37485</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19276; 38057</t>
+          <t>19102; 38199</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23156; 36847</t>
+          <t>24344; 39742</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95666</t>
+          <t>105940</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51690; 72241</t>
+          <t>49719; 73993</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44567; 69964</t>
+          <t>45161; 71663</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43323; 64488</t>
+          <t>44557; 64999</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46020; 66350</t>
+          <t>52421; 72556</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16649; 34700</t>
+          <t>16892; 35436</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31763; 59367</t>
+          <t>31767; 56176</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33670; 62436</t>
+          <t>34196; 60696</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>31765; 47763</t>
+          <t>36380; 54257</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>70432; 104258</t>
+          <t>71300; 103352</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81765; 118811</t>
+          <t>82601; 119601</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82445; 117938</t>
+          <t>81430; 119400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>84524; 109498</t>
+          <t>92447; 121905</t>
         </is>
       </c>
     </row>
